--- a/01_analyses_states/Andaman and Nicobar Islands/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Andaman and Nicobar Islands/results/SoIB_summaries.xlsx
@@ -415,13 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C8">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3">
@@ -706,7 +706,7 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +726,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -778,19 +778,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Trend Different</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>IUCN</t>
         </is>
       </c>
-      <c r="B3">
-        <v>21</v>
-      </c>
-      <c r="C3">
-        <v>20.4</v>
-      </c>
-      <c r="D3">
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>19.4</v>
+      </c>
+      <c r="D4">
         <v>11</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>11.8</v>
       </c>
     </row>

--- a/01_analyses_states/Andaman and Nicobar Islands/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Andaman and Nicobar Islands/results/SoIB_summaries.xlsx
@@ -415,13 +415,13 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="5">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C8">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3">

--- a/01_analyses_states/Andaman and Nicobar Islands/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Andaman and Nicobar Islands/results/SoIB_summaries.xlsx
@@ -398,9 +398,6 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
         <v>0</v>
       </c>
@@ -415,13 +412,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +425,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>100</v>
-      </c>
-      <c r="E4">
-        <v>66.7</v>
       </c>
     </row>
     <row r="5">
@@ -455,9 +446,6 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -474,9 +462,6 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -488,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C8">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +618,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +678,7 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -706,7 +691,7 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +711,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -763,48 +748,35 @@
         </is>
       </c>
       <c r="B2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C2">
-        <v>79.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="D2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2">
-        <v>88.2</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trend Different</t>
+          <t>IUCN</t>
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IUCN</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>19.4</v>
-      </c>
-      <c r="D4">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>11.8</v>
+        <v>22.3</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
